--- a/outputs/daily/hr_rankings_2026-08-15_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-15_full.xlsx
@@ -2214,34 +2214,30 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3330,34 +3326,30 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3614,34 +3606,30 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4174,34 +4162,30 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9182,34 +9166,30 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9740,28 +9720,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y34" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -26564,28 +26548,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W95" t="inlineStr"/>
-      <c r="X95" t="inlineStr"/>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y95" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB95" t="inlineStr"/>
       <c r="AC95" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -35584,28 +35572,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W128" t="inlineStr"/>
-      <c r="X128" t="inlineStr"/>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y128" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB128" t="inlineStr"/>
       <c r="AC128" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -39690,34 +39682,30 @@
       </c>
       <c r="W143" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X143" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y143" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB143" t="inlineStr"/>
       <c r="AC143" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -74388,34 +74376,30 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -75504,34 +75488,30 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -75788,34 +75768,30 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -76348,34 +76324,30 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
